--- a/research/上場不動産会社一覧_2026-08末.xlsx
+++ b/research/上場不動産会社一覧_2026-08末.xlsx
@@ -56,7 +56,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -164,9 +164,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RealEstateList" displayName="RealEstateList" ref="A1:J178" headerRowCount="1">
-  <autoFilter ref="A1:J178"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RealEstateList" displayName="RealEstateList" ref="A1:K178" headerRowCount="1">
+  <autoFilter ref="A1:K178"/>
+  <tableColumns count="11">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="コード"/>
     <tableColumn id="3" name="会社名"/>
@@ -177,6 +177,7 @@
     <tableColumn id="8" name="副分類"/>
     <tableColumn id="9" name="主な事業"/>
     <tableColumn id="10" name="分類の確度"/>
+    <tableColumn id="11" name="根拠（2026年10月に調査した34社）"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
@@ -471,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J178"/>
+  <dimension ref="A1:K178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -482,8 +483,9 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,6 +539,11 @@
           <t>分類の確度</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>根拠（2026年10月に調査した34社）</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -587,6 +594,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -637,6 +645,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -687,6 +696,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -737,6 +747,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -787,6 +798,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -837,6 +849,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -883,6 +896,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -929,6 +943,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -979,6 +994,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1025,6 +1041,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1075,6 +1092,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1121,6 +1139,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1171,6 +1190,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1221,6 +1241,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1267,6 +1288,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1317,6 +1339,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1363,6 +1386,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1409,6 +1433,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1459,6 +1484,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1505,6 +1531,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1551,6 +1578,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1601,54 +1629,60 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>3288</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>オープンハウスグループ</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>プライム</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>戸建て</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>2995</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>ジェイレックス・コーポレーション</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>マンション</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>都市型戸建て・マンション・投資用</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>投資用</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>自社ブランドマンション開発販売（東京）</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>https://jp.investing.com/equities/j-rex-corp</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1692,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>飯田グループホールディングス</t>
+          <t>オープンハウスグループ</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1686,10 +1720,14 @@
           <t>戸建て</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>マンション</t>
+        </is>
+      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>戸建て分譲（国内最大手）</t>
+          <t>都市型戸建て・マンション・投資用</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1697,6 +1735,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1704,12 +1743,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ケイアイスター不動産</t>
+          <t>飯田グループホールディングス</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1735,7 +1774,7 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>戸建て分譲</t>
+          <t>戸建て分譲（国内最大手）</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1743,6 +1782,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1750,12 +1790,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>フジ住宅</t>
+          <t>ケイアイスター不動産</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1778,14 +1818,10 @@
           <t>戸建て</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>マンション</t>
-        </is>
-      </c>
+      <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>戸建て・マンション分譲・賃貸管理（大阪）</t>
+          <t>戸建て分譲</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1793,6 +1829,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1800,12 +1837,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>グランディハウス</t>
+          <t>フジ住宅</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1828,10 +1865,14 @@
           <t>戸建て</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>マンション</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>戸建て分譲（栃木）</t>
+          <t>戸建て・マンション分譲・賃貸管理（大阪）</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1839,6 +1880,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1846,17 +1888,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ヤマイチエステート</t>
+          <t>グランディハウス</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>スタンダード</t>
+          <t>プライム</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1874,21 +1916,18 @@
           <t>戸建て</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>注文住宅</t>
-        </is>
-      </c>
+      <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>戸建て分譲・注文住宅（和歌山）</t>
+          <t>戸建て分譲（栃木）</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1896,12 +1935,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>ホームポジション</t>
+          <t>ヤマイチエステート</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1924,10 +1963,14 @@
           <t>戸建て</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>注文住宅</t>
+        </is>
+      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>戸建て分譲（東海）</t>
+          <t>戸建て分譲・注文住宅（和歌山）</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -1935,6 +1978,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1942,12 +1986,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>アズマハウス</t>
+          <t>ホームポジション</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1970,14 +2014,10 @@
           <t>戸建て</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>アパート・賃貸住宅</t>
-        </is>
-      </c>
+      <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>戸建て分譲・賃貸（和歌山）</t>
+          <t>戸建て分譲（東海）</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -1985,6 +2025,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1992,12 +2033,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>アグレ都市デザイン</t>
+          <t>アズマハウス</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2020,10 +2061,14 @@
           <t>戸建て</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>アパート・賃貸住宅</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>戸建て分譲</t>
+          <t>戸建て分譲・賃貸（和歌山）</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2031,6 +2076,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2038,12 +2084,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>AVANTIA</t>
+          <t>アグレ都市デザイン</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2069,14 +2115,15 @@
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>戸建て分譲（東海）</t>
+          <t>戸建て分譲</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2084,12 +2131,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>ファースト住建</t>
+          <t>AVANTIA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2115,14 +2162,15 @@
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>戸建て分譲（関西）</t>
+          <t>戸建て分譲（東海）</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2130,12 +2178,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>8995</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>誠建設工業</t>
+          <t>ファースト住建</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2161,7 +2209,7 @@
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>戸建て分譲（大阪）</t>
+          <t>戸建て分譲（関西）</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2169,6 +2217,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2176,12 +2225,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>ハウスフリーダム</t>
+          <t>誠建設工業</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2204,14 +2253,10 @@
           <t>戸建て</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>仲介</t>
-        </is>
-      </c>
+      <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>戸建て分譲・仲介（福岡）</t>
+          <t>戸建て分譲（大阪）</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2219,6 +2264,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2226,17 +2272,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>アールプランナー</t>
+          <t>ハウスフリーダム</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>グロース</t>
+          <t>スタンダード</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2256,12 +2302,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>注文住宅</t>
+          <t>仲介</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>戸建て分譲・注文住宅（東京・名古屋）</t>
+          <t>戸建て分譲・仲介（福岡）</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2269,6 +2315,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2276,12 +2323,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>グランディーズ</t>
+          <t>アールプランナー</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2304,10 +2351,14 @@
           <t>戸建て</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>注文住宅</t>
+        </is>
+      </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>戸建て分譲（大分）</t>
+          <t>戸建て分譲・注文住宅（東京・名古屋）</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2315,6 +2366,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2322,12 +2374,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>フォーライフ</t>
+          <t>グランディーズ</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2353,7 +2405,7 @@
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>戸建て分譲</t>
+          <t>戸建て分譲（大分）</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2361,6 +2413,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2368,139 +2421,154 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>アイダ設計</t>
+          <t>フォーライフ</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>グロース</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>戸建て</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>戸建て分譲</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>172A</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>ネオホーム</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
           <t>PRO Market</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>戸建て</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>注文住宅</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>企画戸建住宅の設計・請負・販売（熊本）</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>https://www2.jpx.co.jp/disc/172A0/140120240327560514.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>310A</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>サーティーフォー</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>戸建て</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>注文住宅・分譲住宅</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>1878</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>大東建託</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>プライム</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>アパート・賃貸住宅</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>賃貸住宅の建築・一括借上げ・管理（いい部屋ネット）</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>3276</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>JPMC</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>プライム</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>アパート・賃貸住宅</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>アパートの一括借上げ・管理</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>注文住宅</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>分譲・注文住宅の建築販売（神奈川）</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>https://webtan.impress.co.jp/r/prtimes/items/000000437.000081927</t>
         </is>
       </c>
     </row>
@@ -2510,17 +2578,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>ジェイ・エス・ビー</t>
+          <t>アイダ設計</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>プライム</t>
+          <t>PRO Market</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2535,13 +2603,17 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>アパート・賃貸住宅</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr"/>
+          <t>注文住宅</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>戸建て</t>
+        </is>
+      </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>学生マンションの管理</t>
+          <t>注文住宅・分譲住宅</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -2549,50 +2621,60 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>8848</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>レオパレス21</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>プライム</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>アパート・賃貸住宅</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>アパートの一括借上げ・管理</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>2992</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>アーバンライク</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>注文住宅</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>戸建て</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>注文住宅・戸建、福祉施設建築（熊本）</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>https://compalyze.co.jp/company/4330001017444</t>
         </is>
       </c>
     </row>
@@ -2602,17 +2684,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>robot home</t>
+          <t>大東建託</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>スタンダード</t>
+          <t>プライム</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2630,21 +2712,18 @@
           <t>アパート・賃貸住宅</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>テック</t>
-        </is>
-      </c>
+      <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>投資用アパートの販売・賃貸管理DX</t>
+          <t>賃貸住宅の建築・一括借上げ・管理（いい部屋ネット）</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2652,17 +2731,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>GLC GROUP</t>
+          <t>JPMC</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>スタンダード</t>
+          <t>プライム</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2680,21 +2759,18 @@
           <t>アパート・賃貸住宅</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>投資用</t>
-        </is>
-      </c>
+      <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>賃貸マンションの開発・管理（九州中心）</t>
+          <t>アパートの一括借上げ・管理</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -2702,17 +2778,17 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>長栄</t>
+          <t>ジェイ・エス・ビー</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>スタンダード</t>
+          <t>プライム</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2733,14 +2809,15 @@
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>賃貸管理（京都）</t>
+          <t>学生マンションの管理</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2748,17 +2825,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>香陵住販</t>
+          <t>レオパレス21</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>スタンダード</t>
+          <t>プライム</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2776,21 +2853,18 @@
           <t>アパート・賃貸住宅</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>仲介</t>
-        </is>
-      </c>
+      <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>賃貸管理・仲介（茨城）</t>
+          <t>アパートの一括借上げ・管理</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -2798,12 +2872,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>エリッツホールディングス</t>
+          <t>robot home</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2828,12 +2902,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>仲介</t>
+          <t>テック</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>賃貸仲介・管理（京都）</t>
+          <t>投資用アパートの販売・賃貸管理DX</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -2841,6 +2915,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2848,12 +2923,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>AMGホールディングス</t>
+          <t>GLC GROUP</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2876,10 +2951,14 @@
           <t>アパート・賃貸住宅</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>投資用</t>
+        </is>
+      </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>アパート・マンション建築販売（名古屋）</t>
+          <t>賃貸マンションの開発・管理（九州中心）</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -2887,6 +2966,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -2894,12 +2974,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>毎日コムネット</t>
+          <t>長栄</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2925,14 +3005,15 @@
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>学生マンション</t>
+          <t>賃貸管理（京都）</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2940,12 +3021,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>8945</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>サンネクスタグループ</t>
+          <t>香陵住販</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2968,10 +3049,14 @@
           <t>アパート・賃貸住宅</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>仲介</t>
+        </is>
+      </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>社宅管理代行</t>
+          <t>賃貸管理・仲介（茨城）</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -2979,6 +3064,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -2986,17 +3072,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>アンビション DX ホールディングス</t>
+          <t>エリッツホールディングス</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>グロース</t>
+          <t>スタンダード</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3016,12 +3102,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>投資用</t>
+          <t>仲介</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>賃貸管理・サブリース・投資用</t>
+          <t>賃貸仲介・管理（京都）</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3029,6 +3115,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -3036,17 +3123,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>166A</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>タスキホールディングス</t>
+          <t>AMGホールディングス</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>プライム</t>
+          <t>スタンダード</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3061,17 +3148,13 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>投資用</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>テック</t>
-        </is>
-      </c>
+          <t>アパート・賃貸住宅</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>投資用新築アパート・IoTレジデンス開発</t>
+          <t>アパート・マンション建築販売（名古屋）</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3079,6 +3162,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -3086,17 +3170,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>ADワークスグループ</t>
+          <t>毎日コムネット</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>プライム</t>
+          <t>スタンダード</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3111,13 +3195,13 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>投資用</t>
+          <t>アパート・賃貸住宅</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>一棟収益不動産の販売（富裕層向け）</t>
+          <t>学生マンション</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3125,6 +3209,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -3132,17 +3217,17 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>ディア・ライフ</t>
+          <t>サンネクスタグループ</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>プライム</t>
+          <t>スタンダード</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3157,17 +3242,13 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>投資用</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>マンション</t>
-        </is>
-      </c>
+          <t>アパート・賃貸住宅</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>都市型マンション開発・売却</t>
+          <t>社宅管理代行</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3175,6 +3256,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -3182,17 +3264,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>グッドコムアセット</t>
+          <t>アンビション DX ホールディングス</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>プライム</t>
+          <t>グロース</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3207,64 +3289,74 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
+          <t>アパート・賃貸住宅</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
           <t>投資用</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>投資用マンション</t>
+          <t>賃貸管理・サブリース・投資用</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>3486</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>グローバル・リンク・マネジメント</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>プライム</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>投資用</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>投資用マンション</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>139A</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>東日本地所</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>アパート・賃貸住宅</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr"/>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>地主向け戸建賃貸の建築・管理（埼玉）</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>https://mynavi-agent.jp/corpdetail/41968/</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3366,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>166A</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>ミガロホールディングス</t>
+          <t>タスキホールディングス</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3309,7 +3401,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>投資用マンション・不動産DX</t>
+          <t>投資用新築アパート・IoTレジデンス開発</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3317,6 +3409,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -3324,12 +3417,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>エスリード</t>
+          <t>ADワークスグループ</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3352,14 +3445,10 @@
           <t>投資用</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>マンション</t>
-        </is>
-      </c>
+      <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>投資用・分譲マンション（関西）</t>
+          <t>一棟収益不動産の販売（富裕層向け）</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -3367,6 +3456,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -3374,12 +3464,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>FJネクストホールディングス</t>
+          <t>ディア・ライフ</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3402,17 +3492,22 @@
           <t>投資用</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>マンション</t>
+        </is>
+      </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>投資用マンション（ガーラ）</t>
+          <t>都市型マンション開発・売却</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -3420,17 +3515,17 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>146A</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>コロンビア・ワークス</t>
+          <t>グッドコムアセット</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>スタンダード</t>
+          <t>プライム</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3448,21 +3543,18 @@
           <t>投資用</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>マンション</t>
-        </is>
-      </c>
+      <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>レジデンス・ホテル等の開発</t>
+          <t>投資用マンション</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -3470,17 +3562,17 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>アーバネットコーポレーション</t>
+          <t>グローバル・リンク・マネジメント</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>スタンダード</t>
+          <t>プライム</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3501,7 +3593,7 @@
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>投資用ワンルームマンション開発</t>
+          <t>投資用マンション</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -3509,6 +3601,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -3516,17 +3609,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>アールエイジ</t>
+          <t>ミガロホールディングス</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>スタンダード</t>
+          <t>プライム</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3546,12 +3639,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>アパート・賃貸住宅</t>
+          <t>テック</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>投資用マンション開発・賃貸管理</t>
+          <t>投資用マンション・不動産DX</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -3559,6 +3652,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -3566,17 +3660,17 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>デュアルタップ</t>
+          <t>エスリード</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>スタンダード</t>
+          <t>プライム</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3594,17 +3688,22 @@
           <t>投資用</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>マンション</t>
+        </is>
+      </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>投資用マンション</t>
+          <t>投資用・分譲マンション（関西）</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -3612,17 +3711,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>フェイスネットワーク</t>
+          <t>FJネクストホールディングス</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>スタンダード</t>
+          <t>プライム</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3643,14 +3742,15 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>一棟RCマンション（投資用）</t>
+          <t>投資用マンション（ガーラ）</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -3658,12 +3758,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>146A</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>シーラホールディングス</t>
+          <t>コロンビア・ワークス</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3686,10 +3786,14 @@
           <t>投資用</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>マンション</t>
+        </is>
+      </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>投資用マンション</t>
+          <t>レジデンス・ホテル等の開発</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -3697,6 +3801,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -3704,12 +3809,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>明豊エンタープライズ</t>
+          <t>アーバネットコーポレーション</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3735,60 +3840,66 @@
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>収益マンション開発</t>
+          <t>投資用ワンルームマンション開発</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>3248</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>アールエイジ</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>スタンダード</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>投資用</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>アパート・賃貸住宅</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>投資用マンション開発・賃貸管理</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>5536</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>京橋アートレジデンス</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>投資用</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr"/>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>投資用マンション</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="K69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -3796,17 +3907,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>スター・マイカ・ホールディングス</t>
+          <t>デュアルタップ</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>プライム</t>
+          <t>スタンダード</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3821,20 +3932,21 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>買取再販</t>
+          <t>投資用</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>賃貸中の中古マンションの買取再販</t>
+          <t>投資用マンション</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -3842,17 +3954,17 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>カチタス</t>
+          <t>フェイスネットワーク</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>プライム</t>
+          <t>スタンダード</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3867,20 +3979,21 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>買取再販</t>
+          <t>投資用</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>中古戸建ての買取再販</t>
+          <t>一棟RCマンション（投資用）</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -3888,12 +4001,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>ランドネット</t>
+          <t>シーラホールディングス</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3913,24 +4026,21 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>買取再販</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
           <t>投資用</t>
         </is>
       </c>
+      <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>中古投資用マンションの買取再販</t>
+          <t>投資用マンション</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -3938,12 +4048,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>サンセイランディック</t>
+          <t>明豊エンタープライズ</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3963,260 +4073,290 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>買取再販</t>
+          <t>投資用</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>底地・居抜きなど権利調整型の買取再販</t>
+          <t>収益マンション開発</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>2985</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>ファーストステージ</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>投資用</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>マンション</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>投資用マンション開発・販売（大阪）</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>3297</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>東武住販</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>スタンダード</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>買取再販</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>仲介</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>中古住宅の買取再販・仲介（山口）</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>https://www2.jpx.co.jp/disc/29850/140120230119591164.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>370A</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>リバイブル</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>投資用</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>投資用不動産の企画・開発・販売・管理（東京都千代田区）</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>3299</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>ムゲンエステート</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>スタンダード</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>買取再販</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>https://careerconnection.jp/job/A0223015478349-detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>5528</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>フロンティアハウス</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
         <is>
           <t>投資用</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>中古収益物件の買取再販</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>アパート・賃貸住宅</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>投資用一棟マンション・アパート開発（神奈川県横浜市）</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>https://compalyze.co.jp/company/5020001035096</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>5536</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>京橋アートレジデンス</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>投資用</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>マンション</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>新築一棟収益マンション開発販売（東京23区）</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>https://minkabu.jp/news/4606582</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>617A</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>レイシャス</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>投資用</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>マンション</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>投資用マンションの開発・販売（所在地不明）</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>3490</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>アズ企画設計</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>スタンダード</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>買取再販</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>空室ビル再生・不動産販売</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>463A</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>インテリックスホールディングス</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>スタンダード</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>買取再販</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>中古マンションのリノベ再販</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>5527</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>property technologies</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>グロース</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>買取再販</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>テック</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>中古マンション買取再販×テック</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>https://nihon-ma.co.jp/tokyopromarket/news/w4r-s3mdvc</t>
         </is>
       </c>
     </row>
@@ -4226,17 +4366,17 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>AlbaLink</t>
+          <t>スター・マイカ・ホールディングス</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>グロース</t>
+          <t>プライム</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4257,14 +4397,15 @@
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>訳あり物件の買取再販</t>
+          <t>賃貸中の中古マンションの買取再販</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -4272,12 +4413,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>8919</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>ヒューリック</t>
+          <t>カチタス</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4297,13 +4438,13 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>ビル・商業</t>
+          <t>買取再販</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>オフィス・商業ビル賃貸</t>
+          <t>中古戸建ての買取再販</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -4311,6 +4452,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -4318,17 +4460,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>平和不動産</t>
+          <t>ランドネット</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>プライム</t>
+          <t>スタンダード</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4343,13 +4485,17 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>ビル・商業</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
+          <t>買取再販</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>投資用</t>
+        </is>
+      </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>ビル賃貸（兜町など）</t>
+          <t>中古投資用マンションの買取再販</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -4357,6 +4503,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -4364,17 +4511,17 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>京阪神ビルディング</t>
+          <t>サンセイランディック</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>プライム</t>
+          <t>スタンダード</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4389,20 +4536,21 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>ビル・商業</t>
+          <t>買取再販</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>ビル賃貸（関西）</t>
+          <t>底地・居抜きなど権利調整型の買取再販</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -4410,17 +4558,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>8934</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>サンフロンティア不動産</t>
+          <t>東武住販</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>プライム</t>
+          <t>スタンダード</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4435,24 +4583,25 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>ビル・商業</t>
+          <t>買取再販</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>ファンド・再生</t>
+          <t>仲介</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>オフィス再生・ホテル</t>
+          <t>中古住宅の買取再販・仲介（山口）</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -4460,17 +4609,17 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>日本空港ビルデング</t>
+          <t>ムゲンエステート</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>プライム</t>
+          <t>スタンダード</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4485,13 +4634,17 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>ビル・商業</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr"/>
+          <t>買取再販</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>投資用</t>
+        </is>
+      </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>空港ターミナルビル</t>
+          <t>中古収益物件の買取再販</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -4499,6 +4652,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -4506,12 +4660,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>イノベーションホールディングス</t>
+          <t>アズ企画設計</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4531,13 +4685,13 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>ビル・商業</t>
+          <t>買取再販</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>飲食店舗のサブリース</t>
+          <t>空室ビル再生・不動産販売</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -4545,6 +4699,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -4552,12 +4707,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>8841</t>
+          <t>463A</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>テーオーシー</t>
+          <t>インテリックスホールディングス</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4577,20 +4732,21 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>ビル・商業</t>
+          <t>買取再販</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>ビル賃貸（五反田）</t>
+          <t>中古マンションのリノベ再販</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -4598,17 +4754,17 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>空港施設</t>
+          <t>property technologies</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>スタンダード</t>
+          <t>グロース</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4623,20 +4779,25 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>ビル・商業</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr"/>
+          <t>買取再販</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>テック</t>
+        </is>
+      </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>空港施設の賃貸</t>
+          <t>中古マンション買取再販×テック</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -4644,17 +4805,17 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>ランドビジネス</t>
+          <t>AlbaLink</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>スタンダード</t>
+          <t>グロース</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4669,13 +4830,13 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>ビル・商業</t>
+          <t>買取再販</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>ビル賃貸</t>
+          <t>訳あり物件の買取再販</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -4683,392 +4844,433 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>5532</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>リアルゲイト</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>グロース</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>ビル・商業</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>オフィスビル再生・賃貸</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>301A</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>インデックス</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>買取再販</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr"/>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>中古住宅の仕入・リノベ販売（東京）</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nihon-ma.co.jp/tokyopromarket/news/i4455tq1-r</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>3457</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>And Doホールディングス</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>プライム</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>445A</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>東洋コーポレーション</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>買取再販</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr"/>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>不動産再生事業（千葉県八千代市）</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jpx.co.jp/equities/products/tpm/issues/um3qrc0000027s1w-att/um3qrc0000027s2i.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>490A</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>センス・トラスト</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>買取再販</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>不動産買取・再生加工・販売（大阪府大阪市）</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nihon-ma.co.jp/tokyopromarket/info/2dbkutf_u</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>524A</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>田村ビルズグループ</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>買取再販</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
         <is>
           <t>仲介</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>買取再販・仲介・管理・産廃処理（山口県・福岡県）</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jpx.co.jp/equities/products/tpm/issues/t13vrt000000nuo7-att/t13vrt000000nuot.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>5531</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>エヌバイテクノロジーズ</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
         <is>
           <t>買取再販</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>仲介FC（ハウスドゥ）・リースバック</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>仲介</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>買取再販・仲介・賃貸管理（愛知県名古屋市）※旧中山不動産</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>https://mynavi-agent.jp/corpdetail/21152/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>561A</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>マークスライフ</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>買取再販</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>仲介</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>不動産買取・仲介・活用コンサル（所在地不明）</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>8850</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>スターツコーポレーション</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>プライム</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>仲介</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>アパート・賃貸住宅</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>仲介（ピタットハウス）・賃貸管理・建築</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jpx.co.jp/equities/products/tpm/issues/t13vrt000000shtq-att/t13vrt000000shue.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>595A</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>不二興産</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>買取再販</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>投資用</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>収益不動産の再生・販売（愛知県名古屋市）</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>3241</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>ウィル</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>スタンダード</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>仲介</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>https://prtimes.jp/main/html/rd/p/000000602.000081927.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>8921</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>シーズクリエイト</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
         <is>
           <t>買取再販</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>仲介・リフォーム（兵庫）</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>マンション</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>中古マンション買取再販・一棟開発（東京都渋谷区）</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>8898</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>センチュリー21・ジャパン</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>スタンダード</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>仲介</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>仲介フランチャイズ</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>8912</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>エリアクエスト</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>スタンダード</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>仲介</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>店舗物件の仲介</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>276A</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>ククレブ・アドバイザーズ</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>グロース</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>仲介</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>テック</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>CRE（企業不動産）仲介・情報プラットフォーム</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>2981</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>ランディックス</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>グロース</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>仲介</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>戸建て</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>城南エリアの土地仲介・注文住宅マッチング</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>https://compalyze.co.jp/company/2011001035180</t>
         </is>
       </c>
     </row>
@@ -5078,12 +5280,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>いちご</t>
+          <t>ヒューリック</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -5103,17 +5305,13 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>ファンド・再生</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
           <t>ビル・商業</t>
         </is>
       </c>
+      <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>不動産再生・ファンド・ホテル</t>
+          <t>オフィス・商業ビル賃貸</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -5121,6 +5319,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -5128,12 +5327,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>地主</t>
+          <t>平和不動産</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5153,13 +5352,13 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>ファンド・再生</t>
+          <t>ビル・商業</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>底地（土地）への投資・開発</t>
+          <t>ビル賃貸（兜町など）</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -5167,6 +5366,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -5174,12 +5374,12 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>ロードスターキャピタル</t>
+          <t>京阪神ビルディング</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -5199,24 +5399,21 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>ファンド・再生</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>テック</t>
-        </is>
-      </c>
+          <t>ビル・商業</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>収益不動産・クラウドファンディング</t>
+          <t>ビル賃貸（関西）</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -5224,12 +5421,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>8934</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>霞ヶ関キャピタル</t>
+          <t>サンフロンティア不動産</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -5249,13 +5446,17 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
+          <t>ビル・商業</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
           <t>ファンド・再生</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>物流・ホテル開発ファンド</t>
+          <t>オフィス再生・ホテル</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -5263,6 +5464,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -5270,12 +5472,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9706</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>トーセイ</t>
+          <t>日本空港ビルデング</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -5295,17 +5497,13 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>ファンド・再生</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>マンション</t>
-        </is>
-      </c>
+          <t>ビル・商業</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>不動産再生・ファンド・開発</t>
+          <t>空港ターミナルビル</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -5313,6 +5511,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -5320,12 +5519,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>ファンドクリエーショングループ</t>
+          <t>イノベーションホールディングス</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -5345,13 +5544,13 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>ファンド・再生</t>
+          <t>ビル・商業</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>ファンド・アセットマネジメント</t>
+          <t>飲食店舗のサブリース</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -5359,50 +5558,56 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="3" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>3452</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>ビーロット</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>8836</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>RISE</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>スタンダード</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>ファンド・再生</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>不動産再生・投資</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>ビル・商業</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr"/>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>不動産賃貸・不動産管理</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
         <is>
           <t>中</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>https://irbank.net/E00165</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5617,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>8841</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>ファーストブラザーズ</t>
+          <t>テーオーシー</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -5437,13 +5642,13 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>ファンド・再生</t>
+          <t>ビル・商業</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>不動産投資・アセットマネジメント</t>
+          <t>ビル賃貸（五反田）</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -5451,6 +5656,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -5458,12 +5664,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>マリオン</t>
+          <t>空港施設</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -5483,20 +5689,21 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>ファンド・再生</t>
+          <t>ビル・商業</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>賃貸不動産・小口化商品</t>
+          <t>空港施設の賃貸</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -5504,12 +5711,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>8944</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>ウェルス・マネジメント</t>
+          <t>ランドビジネス</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -5529,13 +5736,13 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>ファンド・再生</t>
+          <t>ビル・商業</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>ホテル開発・アセットマネジメント</t>
+          <t>ビル賃貸</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -5543,6 +5750,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -5550,17 +5758,17 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>青山財産ネットワークス</t>
+          <t>リアルゲイト</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>スタンダード</t>
+          <t>グロース</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5575,13 +5783,13 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>ファンド・再生</t>
+          <t>ビル・商業</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>資産コンサル・不動産小口化</t>
+          <t>オフィスビル再生・賃貸</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -5589,200 +5797,213 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="3" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>3237</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>イントランス</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>グロース</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>3483</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>翔栄</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>ビル・商業</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr"/>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>賃貸・投資開発・仲介（東京・名古屋）</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>https://www2.jpx.co.jp/disc/34830/140120260721597055.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>358A</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>ゼン・ランド</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>ビル・商業</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr"/>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>商業用不動産・ビルの取扱い（東京）</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jpx.co.jp/equities/products/tpm/issues/um3qrc00000166z3-att/um3qrc00000166zm.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>434A</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>LOOPLACE</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>ビル・商業</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
         <is>
           <t>ファンド・再生</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>不動産再生・ホテル</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>2980</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>SREホールディングス</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>プライム</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>テック</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>仲介</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>不動産仲介×AIソリューション</t>
-        </is>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>築古ビル再生・建築マネジメント（東京都千代田区）</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>2978</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>ツクルバ</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>グロース</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>テック</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>買取再販</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>リノベ中古マンション流通サイト（カウカモ）</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jpx.co.jp/equities/products/tpm/issues/um3qrc0000023o3g-att/um3qrc0000023o42.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>614A</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>山八商事</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>ビル・商業</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr"/>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>商業用不動産の開発・賃貸・売却（愛知県蒲郡市）</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>2998</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>クリアル</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>グロース</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>テック</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>ファンド・再生</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>不動産クラウドファンディング</t>
-        </is>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jpx.co.jp/equities/products/tpm/issues/t13vrt000001jfzr-att/t13vrt000001jg0f.pdf</t>
         </is>
       </c>
     </row>
@@ -5792,17 +6013,17 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>GA technologies</t>
+          <t>And Doホールディングス</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>グロース</t>
+          <t>プライム</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -5817,17 +6038,17 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>テック</t>
+          <t>仲介</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>投資用</t>
+          <t>買取再販</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>不動産テック（RENOSY）</t>
+          <t>仲介FC（ハウスドゥ）・リースバック</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -5835,6 +6056,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -5842,12 +6064,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>日本駐車場開発</t>
+          <t>スターツコーポレーション</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -5867,13 +6089,17 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>駐車場・スペース</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr"/>
+          <t>仲介</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>アパート・賃貸住宅</t>
+        </is>
+      </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>駐車場の転貸運営</t>
+          <t>仲介（ピタットハウス）・賃貸管理・建築</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -5881,6 +6107,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -5888,17 +6115,17 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>アズーム</t>
+          <t>ウィル</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>プライム</t>
+          <t>スタンダード</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -5913,20 +6140,25 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>駐車場・スペース</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr"/>
+          <t>仲介</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>買取再販</t>
+        </is>
+      </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>月極駐車場のサブリース</t>
+          <t>仲介・リフォーム（兵庫）</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -5934,17 +6166,17 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>パーク24</t>
+          <t>センチュリー21・ジャパン</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>プライム</t>
+          <t>スタンダード</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -5959,13 +6191,13 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>駐車場・スペース</t>
+          <t>仲介</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>時間貸駐車場（タイムズ）</t>
+          <t>仲介フランチャイズ</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -5973,6 +6205,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -5980,17 +6213,17 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>パラカ</t>
+          <t>エリアクエスト</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>プライム</t>
+          <t>スタンダード</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6005,20 +6238,21 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>駐車場・スペース</t>
+          <t>仲介</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>駐車場</t>
+          <t>店舗物件の仲介</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -6026,17 +6260,17 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>276A</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>トラストホールディングス</t>
+          <t>ククレブ・アドバイザーズ</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>スタンダード</t>
+          <t>グロース</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6051,13 +6285,17 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>駐車場・スペース</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr"/>
+          <t>仲介</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>テック</t>
+        </is>
+      </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>駐車場ほか（福岡）</t>
+          <t>CRE（企業不動産）仲介・情報プラットフォーム</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -6065,6 +6303,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -6072,17 +6311,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>パルマ</t>
+          <t>ランディックス</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>スタンダード</t>
+          <t>グロース</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6097,13 +6336,17 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>駐車場・スペース</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr"/>
+          <t>仲介</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>戸建て</t>
+        </is>
+      </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>トランクルーム関連</t>
+          <t>城南エリアの土地仲介・注文住宅マッチング</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -6111,146 +6354,170 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>8914</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>エリアリンク</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>スタンダード</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>駐車場・スペース</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>ファンド・再生</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>トランクルーム・底地</t>
-        </is>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>239A</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>バレッグス</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>仲介</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>買取再販</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>賃貸・売買仲介、管理、仕入再販（東京）</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>https://hrmos.co/pages/balleggs/jobs/0000024</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>2997</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>ストレージ王</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>グロース</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>駐車場・スペース</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>トランクルーム</t>
-        </is>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>2994</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>アンサーホールディングス</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>仲介</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>買取再販</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>売買仲介・買取再販・賃貸管理（北九州）</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>https://data-max.co.jp/article/64894</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>3479</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>TKP</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>グロース</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>駐車場・スペース</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr"/>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>貸会議室</t>
-        </is>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>5525</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>フロンティアホールディングス</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>PRO Market</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>仲介</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>戸建て</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>住宅売買仲介・戸建て販売・リフォーム（大阪府）</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>https://www.onecareer.jp/companies/95991</t>
         </is>
       </c>
     </row>
@@ -6260,12 +6527,12 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>164A</t>
+          <t>583A</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>アップルパーク</t>
+          <t>不動産流通システム</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -6285,18 +6552,23 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>駐車場・スペース</t>
+          <t>仲介</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr"/>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>駐車場運営</t>
+          <t>不動産売買仲介・リフォーム（東京都新宿区）</t>
         </is>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nihon-ma.co.jp/tokyopromarket/news/di4g5km90g</t>
         </is>
       </c>
     </row>
@@ -6306,12 +6578,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>三重交通グループホールディングス</t>
+          <t>いちご</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -6331,13 +6603,17 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr"/>
+          <t>ファンド・再生</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>ビル・商業</t>
+        </is>
+      </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>交通・不動産（分譲・賃貸）</t>
+          <t>不動産再生・ファンド・ホテル</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -6345,6 +6621,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -6352,12 +6629,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>宮越ホールディングス</t>
+          <t>地主</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -6377,66 +6654,72 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>ファンド・再生</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>海外（中国）での不動産開発</t>
+          <t>底地（土地）への投資・開発</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
+      <c r="A125" s="2" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>1783</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>fantasista</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>スタンダード</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H125" s="3" t="inlineStr"/>
-      <c r="I125" s="3" t="inlineStr">
-        <is>
-          <t>不動産販売ほか</t>
-        </is>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>3482</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>ロードスターキャピタル</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>プライム</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>ファンド・再生</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>テック</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>収益不動産・クラウドファンディング</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -6444,17 +6727,17 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>JALCOホールディングス</t>
+          <t>霞ヶ関キャピタル</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>スタンダード</t>
+          <t>プライム</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6469,112 +6752,119 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>ファンド・再生</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr"/>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>不動産賃貸・貸金</t>
+          <t>物流・ホテル開発ファンド</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>8923</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>トーセイ</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>プライム</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>ファンド・再生</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>マンション</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>不動産再生・ファンド・開発</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>3266</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>ファンドクリエーショングループ</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>スタンダード</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>ファンド・再生</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>ファンド・アセットマネジメント</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>8836</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>RISE</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>スタンダード</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F127" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G127" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H127" s="3" t="inlineStr"/>
-      <c r="I127" s="3" t="inlineStr">
-        <is>
-          <t>不動産賃貸ほか</t>
-        </is>
-      </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>8894</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>REVOLUTION</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>スタンダード</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F128" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G128" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="inlineStr"/>
-      <c r="I128" s="3" t="inlineStr">
-        <is>
-          <t>不動産ほか</t>
-        </is>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="K128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -6582,12 +6872,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>8946</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>ASIAN STAR</t>
+          <t>ビーロット</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -6607,13 +6897,13 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>ファンド・再生</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr"/>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>賃貸管理ほか（中国）</t>
+          <t>不動産再生・投資</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
@@ -6621,6 +6911,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -6628,12 +6919,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>9633</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>東京テアトル</t>
+          <t>ファーストブラザーズ</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -6653,13 +6944,13 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>ファンド・再生</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr"/>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>映画館・不動産賃貸</t>
+          <t>不動産投資・アセットマネジメント</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -6667,6 +6958,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -6674,12 +6966,12 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>9816</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>ストライダーズ</t>
+          <t>マリオン</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -6699,13 +6991,13 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>ファンド・再生</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr"/>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>ホテル・不動産</t>
+          <t>賃貸不動産・小口化商品</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -6713,6 +7005,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -6720,12 +7013,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>エムティジェネックス</t>
+          <t>ウェルス・マネジメント</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -6745,13 +7038,13 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>ファンド・再生</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr"/>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>ビル管理ほか</t>
+          <t>ホテル開発・アセットマネジメント</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -6759,742 +7052,783 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>3474</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>G-FACTORY</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>8894</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>REVOLUTION</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>スタンダード</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>ファンド・再生</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr"/>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>不動産販売・担保融資・不動産CF</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>https://j-lic.com/companies/8894</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>8929</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>青山財産ネットワークス</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>スタンダード</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>ファンド・再生</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>資産コンサル・不動産小口化</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>3237</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>イントランス</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>グロース</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr"/>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t>飲食店舗のサブリースほか</t>
-        </is>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>ファンド・再生</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>不動産再生・ホテル</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>8938</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>グローム・ホールディングス</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="K135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>SREホールディングス</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>プライム</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>テック</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>仲介</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>不動産仲介×AIソリューション</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>2978</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>ツクルバ</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>グロース</t>
         </is>
       </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F134" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G134" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H134" s="3" t="inlineStr"/>
-      <c r="I134" s="3" t="inlineStr">
-        <is>
-          <t>医療関連ほか</t>
-        </is>
-      </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>139A</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>東日本地所</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F135" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G135" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H135" s="3" t="inlineStr"/>
-      <c r="I135" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="3" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>172A</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>ネオホーム</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G136" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H136" s="3" t="inlineStr"/>
-      <c r="I136" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>239A</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>バレッグス</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G137" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H137" s="3" t="inlineStr"/>
-      <c r="I137" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J137" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>テック</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>買取再販</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>リノベ中古マンション流通サイト（カウカモ）</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n">
+      <c r="A138" s="2" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>2985</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t>ファーストステージ</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E138" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F138" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G138" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H138" s="3" t="inlineStr"/>
-      <c r="I138" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>クリアル</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>グロース</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>テック</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>ファンド・再生</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>不動産クラウドファンディング</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n">
+      <c r="A139" s="2" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>2992</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>アーバンライク</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F139" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G139" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H139" s="3" t="inlineStr"/>
-      <c r="I139" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>GA technologies</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>グロース</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>テック</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>投資用</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>不動産テック（RENOSY）</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n">
+      <c r="A140" s="2" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>2994</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>アンサーホールディングス</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F140" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G140" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H140" s="3" t="inlineStr"/>
-      <c r="I140" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>日本駐車場開発</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>プライム</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>駐車場・スペース</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>駐車場の転貸運営</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="n">
+      <c r="A141" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>2995</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t>ジェイレックス・コーポレーション</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G141" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H141" s="3" t="inlineStr"/>
-      <c r="I141" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>3496</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>アズーム</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>プライム</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>駐車場・スペース</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr"/>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>月極駐車場のサブリース</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="n">
+      <c r="A142" s="2" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>301A</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="inlineStr">
-        <is>
-          <t>インデックス</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E142" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F142" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G142" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H142" s="3" t="inlineStr"/>
-      <c r="I142" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>4666</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>パーク24</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>プライム</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>駐車場・スペース</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>時間貸駐車場（タイムズ）</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="n">
+      <c r="A143" s="2" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>310A</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>サーティーフォー</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F143" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G143" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H143" s="3" t="inlineStr"/>
-      <c r="I143" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>4809</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>パラカ</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>プライム</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>駐車場・スペース</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>駐車場</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="n">
+      <c r="A144" s="2" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>3483</t>
-        </is>
-      </c>
-      <c r="C144" s="3" t="inlineStr">
-        <is>
-          <t>翔栄</t>
-        </is>
-      </c>
-      <c r="D144" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E144" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F144" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G144" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H144" s="3" t="inlineStr"/>
-      <c r="I144" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>3286</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>トラストホールディングス</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>スタンダード</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>駐車場・スペース</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>駐車場ほか（福岡）</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="n">
+      <c r="A145" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>358A</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t>ゼン・ランド</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G145" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H145" s="3" t="inlineStr"/>
-      <c r="I145" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>3461</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>パルマ</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>スタンダード</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>駐車場・スペース</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr"/>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>トランクルーム関連</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="n">
+      <c r="A146" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>370A</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t>リバイブル</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G146" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H146" s="3" t="inlineStr"/>
-      <c r="I146" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>8914</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>エリアリンク</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>スタンダード</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>駐車場・スペース</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>ファンド・再生</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>トランクルーム・底地</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="n">
+      <c r="A147" s="2" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>375A</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr">
-        <is>
-          <t>YAKホールディングス</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E147" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F147" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G147" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H147" s="3" t="inlineStr"/>
-      <c r="I147" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>2997</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>ストレージ王</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>グロース</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>駐車場・スペース</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>トランクルーム</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="n">
+      <c r="A148" s="2" t="n">
         <v>147</v>
       </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>434A</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="inlineStr">
-        <is>
-          <t>LOOPLACE</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F148" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G148" s="3" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="H148" s="3" t="inlineStr"/>
-      <c r="I148" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>TKP</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>グロース</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>駐車場・スペース</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr"/>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>貸会議室</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
@@ -7502,12 +7836,12 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>445A</t>
+          <t>164A</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>東洋コーポレーション</t>
+          <t>アップルパーク</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -7527,112 +7861,119 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>駐車場・スペース</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr"/>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>事業内容未確認（PRO Market）</t>
+          <t>駐車場・駐輪場の運営管理（東京都北区）</t>
         </is>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>https://www.r-agent.com/company/85920/</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="n">
+      <c r="A150" s="2" t="n">
         <v>149</v>
       </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>458A</t>
-        </is>
-      </c>
-      <c r="C150" s="3" t="inlineStr">
-        <is>
-          <t>プラン・ドゥ</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F150" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G150" s="3" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>3232</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>三重交通グループホールディングス</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>プライム</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr"/>
-      <c r="I150" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="H150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>交通・不動産（分譲・賃貸）</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="n">
+      <c r="A151" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>490A</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t>センス・トラスト</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G151" s="3" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>6620</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>宮越ホールディングス</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>プライム</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="H151" s="3" t="inlineStr"/>
-      <c r="I151" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="H151" s="2" t="inlineStr"/>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>海外（中国）での不動産開発</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
@@ -7640,17 +7981,17 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>524A</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>田村ビルズグループ</t>
+          <t>fantasista</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>PRO Market</t>
+          <t>スタンダード</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
@@ -7671,290 +8012,301 @@
       <c r="H152" s="3" t="inlineStr"/>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>事業内容未確認（PRO Market）</t>
+          <t>不動産売買・保有・ホテル民泊運営等（東京）</t>
         </is>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>https://finboard.jp/companies/JP:1783/segments</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="3" t="n">
+      <c r="A153" s="2" t="n">
         <v>152</v>
       </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>5525</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="inlineStr">
-        <is>
-          <t>フロンティアホールディングス</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F153" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G153" s="3" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>6625</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>JALCOホールディングス</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>スタンダード</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr"/>
-      <c r="I153" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="H153" s="2" t="inlineStr"/>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>不動産賃貸・貸金</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="3" t="n">
+      <c r="A154" s="2" t="n">
         <v>153</v>
       </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>5528</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="inlineStr">
-        <is>
-          <t>フロンティアハウス</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F154" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G154" s="3" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>8946</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>ASIAN STAR</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>スタンダード</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr"/>
-      <c r="I154" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="H154" s="2" t="inlineStr"/>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>賃貸管理ほか（中国）</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="n">
+      <c r="A155" s="2" t="n">
         <v>154</v>
       </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>5531</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="inlineStr">
-        <is>
-          <t>エヌバイテクノロジーズ</t>
-        </is>
-      </c>
-      <c r="D155" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E155" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F155" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G155" s="3" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>9633</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>東京テアトル</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>スタンダード</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="H155" s="3" t="inlineStr"/>
-      <c r="I155" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="H155" s="2" t="inlineStr"/>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>映画館・不動産賃貸</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="n">
+      <c r="A156" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t>5534</t>
-        </is>
-      </c>
-      <c r="C156" s="3" t="inlineStr">
-        <is>
-          <t>エンゼルグループ</t>
-        </is>
-      </c>
-      <c r="D156" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E156" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F156" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G156" s="3" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>9816</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>ストライダーズ</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>スタンダード</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr"/>
-      <c r="I156" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="H156" s="2" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>ホテル・不動産</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="3" t="n">
+      <c r="A157" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>561A</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>マークスライフ</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F157" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G157" s="3" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>9820</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>エムティジェネックス</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>スタンダード</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="H157" s="3" t="inlineStr"/>
-      <c r="I157" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="H157" s="2" t="inlineStr"/>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>ビル管理ほか</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="3" t="n">
+      <c r="A158" s="2" t="n">
         <v>157</v>
       </c>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>583A</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="inlineStr">
-        <is>
-          <t>不動産流通システム</t>
-        </is>
-      </c>
-      <c r="D158" s="3" t="inlineStr">
-        <is>
-          <t>PRO Market</t>
-        </is>
-      </c>
-      <c r="E158" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="F158" s="3" t="inlineStr">
-        <is>
-          <t>不動産業</t>
-        </is>
-      </c>
-      <c r="G158" s="3" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>3474</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>G-FACTORY</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>グロース</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>不動産業</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr"/>
-      <c r="I158" s="3" t="inlineStr">
-        <is>
-          <t>事業内容未確認（PRO Market）</t>
-        </is>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>飲食店舗のサブリースほか</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
@@ -7962,17 +8314,17 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>595A</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>不二興産</t>
+          <t>グローム・ホールディングス</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>PRO Market</t>
+          <t>グロース</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
@@ -7990,15 +8342,24 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="H159" s="3" t="inlineStr"/>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>ビル・商業</t>
+        </is>
+      </c>
       <c r="I159" s="3" t="inlineStr">
         <is>
-          <t>事業内容未確認（PRO Market）</t>
+          <t>医療機関経営支援が主、不動産縮小（東京）</t>
         </is>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>https://j-lic.com/companies/8938</t>
         </is>
       </c>
     </row>
@@ -8008,12 +8369,12 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>614A</t>
+          <t>375A</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>山八商事</t>
+          <t>YAKホールディングス</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -8036,15 +8397,24 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr"/>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>投資用</t>
+        </is>
+      </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>事業内容未確認（PRO Market）</t>
+          <t>インバウンド向け不動産総合事業（東京都台東区）</t>
         </is>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nihon-ma.co.jp/page/250620_information/</t>
         </is>
       </c>
     </row>
@@ -8054,12 +8424,12 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>617A</t>
+          <t>458A</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>レイシャス</t>
+          <t>プラン・ドゥ</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -8085,12 +8455,17 @@
       <c r="H161" s="3" t="inlineStr"/>
       <c r="I161" s="3" t="inlineStr">
         <is>
-          <t>事業内容未確認（PRO Market）</t>
+          <t>不動産の売買・賃貸・管理（東京都千代田区）</t>
         </is>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jpx.co.jp/equities/products/tpm/issues/um3qrc00000289kp-att/um3qrc00000289lb.pdf</t>
         </is>
       </c>
     </row>
@@ -8100,12 +8475,12 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>シーズクリエイト</t>
+          <t>エンゼルグループ</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -8128,15 +8503,24 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="H162" s="3" t="inlineStr"/>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>仲介</t>
+        </is>
+      </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>事業内容未確認（PRO Market）</t>
+          <t>リゾートホテル・別荘地管理・仲介（新潟県南魚沼郡）</t>
         </is>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>https://www2.jpx.co.jp/disc/55340/140120230920556376.pdf</t>
         </is>
       </c>
     </row>
@@ -8185,6 +8569,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -8231,6 +8616,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -8277,6 +8663,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -8323,6 +8710,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -8373,6 +8761,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -8423,6 +8812,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -8473,6 +8863,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -8519,6 +8910,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -8569,6 +8961,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -8615,6 +9008,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -8661,6 +9055,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -8707,6 +9102,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -8753,6 +9149,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -8799,6 +9196,7 @@
           <t>中</t>
         </is>
       </c>
+      <c r="K176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -8845,6 +9243,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -8891,6 +9290,7 @@
           <t>高</t>
         </is>
       </c>
+      <c r="K178" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9253,7 +9653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -9290,7 +9690,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>「主分類」「副分類」「主な事業」はClaudeの知識による分類で、各社IRでの裏取りはしていない。「分類の確度」が「要確認」の行（黄色）は事業内容を把握できていない会社。</t>
+          <t>「主分類」「副分類」「主な事業」はClaudeの知識による分類で、各社IRでの裏取りはしていない。2026年10月、当初「要確認」だった34社（主にTOKYO PRO Market）を検索で調査し、分類・事業内容を更新した（緑色の行。K列に根拠URL）。検索結果の抜粋に基づく判断で、各社の開示書類の精読まではしていない。</t>
         </is>
       </c>
     </row>
@@ -9312,6 +9712,13 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>2026年8月末以降の新規上場・上場廃止は反映されていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>調査メモ：5531エヌバイテクノロジーズは2026年6月に中山不動産から社名変更。8938グローム・ホールディングスは医療関連が主力で不動産は縮小中。561Aマークスライフ・617Aレイシャスは本社所在地を確認できず。</t>
         </is>
       </c>
     </row>
